--- a/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
@@ -17,6 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초음파_참고" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1055,650 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>`_구판_v2.6/` 보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. ARI-Core 77.5 ± 0 (B)·SI 75 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile ST36; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>초음파_참고 시트·그림 4-2 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>앞정강근 공개 초음파 통계, 1896 TI, Rank 6 재실행 로그. 점수 불변</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Marzola 2021; PMID 42500462</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>긴발가락폄근 (extensor digitorum longus)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22534</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Extensor digitorum longus</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FMA:80068 Nerve to extensor digitorum longus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Medial terminal branch of deep fibular nerve → Deep fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>L5(primary/segmental), S1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>위와 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>앞정강근 (tibialis anterior)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22532</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tibialis anterior</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FMA:80062 Nerve to tibialis anterior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medial terminal branch of deep fibular nerve → Deep fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>L4(primary/segmental), L5(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>근육가지 기원: FMA는 안쪽종말가지로 기록 → 깊은종아리신경 수준만 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>깊은종아리신경 (deep fibular nerve); 깊은종아리신경 (deep peroneal nerve)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>44771</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Deep fibular nerve</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>가쪽장딴지피부신경 (lateral sural cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>44697</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lateral sural cutaneous nerve</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>두렁신경의 안쪽종아리피부가지 (medial crural cutaneous branch of the saphenous nerve)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>75559</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Set of medial crural cutaneous branches of saphenous nerve</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>두렁신경→넙다리신경 연결 FMA 미기재(B1 보완)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>얕은종아리신경 (superficial peroneal nerve)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>44699</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Superficial fibular nerve</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>앞정강동ㆍ정맥 (anterior tibial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>43894</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Anterior tibial artery</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FMA:18805 External iliac artery → FMA:14764 Common iliac artery</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FMA는 오금동맥을 바깥엉덩동맥 연속 구간으로 모델링</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>앞정강동ㆍ정맥 (anterior tibial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>44331</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Anterior tibial vein</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FMA:44327 Popliteal vein → FMA:51041 Deep femoral vein → FMA:21185 Femoral vein → FMA:18883 External iliac vein → FMA:14333 Common iliac vein → FMA:10951 Inferior vena cava</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L4, L5, S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>공통 6 · 공통교재 단독 1 · 김재효 단독 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile ST36 (2026-10-23). B1 보조(등록부 미등재)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marzola F et al. Comput Biol Med 2021;135:104623, dataset doi:10.17632/3jykz7wz8d.1 (CC BY 4.0)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>공개 데이터, ST36 직접 촬영 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건강군 영상 수</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3092</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>피험자 수</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1021</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>단면적 중앙값(px²)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52589.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>사분위 41396.5–63966.75; mm 보정 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>평균 회색조 중앙값</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>78</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>사분위 67.8–87.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>내부/주변 에코비 중앙값</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>예시 영상</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>anon_1669_3.png</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>papers.id 1896</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TI ST36 1.09 / GB21 1.54</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Choi 2026 Integr Med Res, PMID 42500462, 39명 탐색 연구</t>
         </is>
       </c>
     </row>

--- a/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초음파_참고" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초음파_참고" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +50,9 @@
     <font>
       <b val="1"/>
       <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -96,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +109,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +609,455 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7 추가 — 4대 원전 대조(《经络通鉴》·《证治通鉴》 한글번역·《通考》 현행 편 행). 위 v2.6 행과 별개, 정본은 .md·ARI_v3.0 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>문헌</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>출처 파일</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>행</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>층차</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>판정·용도</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 明堂 足三里 주치(원문·한글번역)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>腹中寒，胀满，善噫，恶闻食臭，胃气不足，肠鸣腹痛，泄利，食不化，心下胀 / 뱃속이 차고 창만한 것, 트림을 잘하는 것…</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_04_第壹编_第七篇_手太阴肺经_手阳明大肠经_足阳明胃经.md ; …_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>L926 ; L1213</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>한대</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>P_single 기술(한글 번역본 기준, 불일치 없음)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>구 포인터 PDF 1–80 L2162~2166</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 喉痹 冲脉·三里(원문·按·한글번역)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>喉痹，胸中暴逆，先取冲脉，后取三里、云门，皆泻之 / 按：冲脉应是气冲, 三里应是足三里</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_03_第壹编_第五至六篇_禁咒之法_古代针灸方选解.md ; …_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>L268, L270 ; L412~416</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>한대</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>P_comb</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>구 포인터 PDF 1–80 L1242; 02편 L136·번역 L177 동문</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 灵枢·经脉 足阳明 胫外廉</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>下循胫外廉 — 谓胫骨之外廉也。其外廉下膝三寸，三里穴也(医学纲目)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_19_第叁编_第三篇_足阳明经脉、经别、络脉和经筋(一~二).md</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>L253</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대(주: 명)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>경맥 순행·명칭 — 해당 혈 정위 신규 정보 없음</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Target 1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 本输·太素 杨上善</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>入于下陵，下陵，膝下三寸，胻骨外三里也 / 以在胻骨外侧，故名为廉。足阳明脉行此虚中</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_19_第叁编_第三篇_足阳明经脉、经别、络脉和经筋(一~二).md</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>L445, L449</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대 / 수당</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>廉 = 정강뼈 바깥쪽</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Target 1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11편 L567·L571 동문</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 下合穴</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>胃合于三里… / 六腑下合穴之说留下了理论空间 / 具有较充分的临床实践基础 / 胃病者…取之三里也</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_03_第壹编_第二篇_经络学说的演变(八~十一).md</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>L932, L934, L1203, L1205, L1211</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>하합혈 = 경락론적 틀(기전 근거 아님)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 根结 下陵 개찬</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>足阳明…注于下陵 / 【按】马注…将足阳明下陵改作解溪…下陵原指足三里</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_13_第贰编_第五篇_经络的根结、关阖枢与皮部.md</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>L167, L186</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대 / 명(马莳)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Rank 4 주석 개찬 교정</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3절 下陵</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 王冰 足阳明→三里 귀속</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>热病始足胫者，刺足阳明 → 三里主之 / 胃疟 → 厉兑、解溪、三里主之 / 骨空论 → 正取三里穴; 杨上善 巨虚上廉; 【按】不仅限于三里</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_20_第叁编_第三篇_足阳明经脉、经别、络脉和经筋(三).md</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>L240~247, L1384, L2434, L2438, L2452</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>당</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Rank 4 경맥 조문 혈위 귀속 — 혈 고유 주치로 미사용</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 经脉穴 대응</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>足阳明——冲阳</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>L789</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>한대(고증)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>한대 경맥혈 = 冲阳(三里 아님)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 马莳 本输 주 심도</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>三里穴也，为合土，针五分，留五呼</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>L580</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5절 보조 심도 5푼</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>通考 횡향 계통(현행 편)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>胻外两筋肉分间。极重按之，则足跗上动脉止(王冰 등) / 胻外廉两筋间(铜人卷下·圣济) / 胻骨外大筋内 / 文献分析: 王冰 过于偏外侧, 圣惠 过于偏内侧, 现代 胫骨前肌中</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>침구수혈통고(针灸腧穴通考)/针灸腧穴通考_08_上_足阳明胃经穴-3.md</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>L215, L231, L239~259, L295, L307</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>당~현대</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 표현 원천 / 현대 部位 胻外廉 유지</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Target 2 / Target 1≡3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>보고서 본문 通考 L3198 등은 구 PDF 청크 행번호</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -615,490 +1069,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>원래 내용</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>바꾼 내용</t>
+          <t>X (정강뼈 앞모서리 기준 외측)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Z / Δ(추정)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>근거·판정</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>머리말</t>
+          <t>Target 1 (고전 문헌)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>프레임워크 문구, "실측 논문 148편 전수 역색인"</t>
+          <t>灵枢·本输·明堂 膝下三寸，胻外(廉) — 주가 胫骨之外廉</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>v2.7 인용 블록, ARI 표기 / 근거 묶음 수치(38·109·39)로 교체</t>
+          <t>약 0.5~1.5cm (원문 횡향 미특정)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>final_ST36.json notation, pack_ST36.md</t>
+          <t>膝下 3寸</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1寸 23mm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>经络通鉴 19편 L253·L449; 通考 L307</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1절</t>
+          <t>Target 2 (촉진 실체화·자입 기준점)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>通鉴 목차 조각, 证治通鉴 冲脉 고증 문단, 通考 목차 조각</t>
+          <t>王冰 胻外两筋肉分间 / 铜人卷下·圣济 胻外廉两筋间 = 앞정강근(FMA:22532)–긴발가락폄근(FMA:22534) 근간 중격</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>《灵枢·本输》·《素问·针解》·《明堂》 원문과 출처 행</t>
+          <t>약 2.5~3.5cm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>通考 `(上)_321-400.md` L3096~3248; 通鉴 `(上卷)_801-880.md` L3410~3692; 证治通鉴 `_1-80.md` L1242, L2162</t>
+          <t>膝下 3寸</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>중격 깊이 → FMA:44771·43894·44331, 바닥 FMA:35187</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>通考 L215·L231 (현행 편)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2절</t>
+          <t>Target 3 (WHO)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>제목뿐인 템플릿</t>
+          <t>犊鼻下3寸, 犊鼻–解溪 연결선, 胫骨前嵴 외측 1횡지, 앞정강근 中</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>시대별 원천/재인용 표</t>
+          <t>약 1.5~2cm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>같은 원전</t>
+          <t>犊鼻下 3寸</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>직자 1~2寸 23~46mm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>通考 L295</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3절</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>"검증된 고전 이명: -"</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>三里·下陵·鬼邪·下三里 표</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>KJH xlsx 행 122; 通考 L3096~3146; 通鉴 L3412~3428</t>
+          <t>Δ T1–T3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>약 0~10mm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>병합 — 현대 部位 "在膝下三寸，胻外廉" 유지, 取穴만 一横指로 구체화</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4절</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>범용 Layer 경계 2.5/6.5/16.5/22mm, 'Layer 5 관절낭'</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ST36 구조 순서(앞정강근→깊은종아리신경·앞정강동정맥→뼈사이막), X·Y 기술, mm 경계는 실측 없음으로 미기재</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>교재 데이터셋; 通考 L3114~3116</t>
+          <t>Δ T2–T3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>약 10~15mm (범위 5~20)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>분기(경계값) — 앞정강근 표면 폭 2.5~3.5cm·중지 폭 1.5~2cm 추정; ST36 높이 폭 실측 없음</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5절</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>공식 설명만</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>문헌별 푼수→mm 계산표</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>자침깊이 xlsx 행 121; 通鉴 L3676~3692</t>
+          <t>Δ T1–T2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>약 10~25mm</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>분기</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6절</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"2대 교재 일치" 일반문</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>실제 구조명, 피부신경 차이 명시</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>공통교재 refine.xlsx 상세 행 650~655; 김재효 xlsx 상세 행 954~959</t>
+          <t>Target 1≡3 vs Target 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>분기 기준 Δ &gt; 10mm</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10mm 기준으로 T2–T3 쌍이 병합→분기로 바뀜(15mm 기준이면 병합)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7절</t>
+          <t>내측 계통</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>규칙 설명만</t>
+          <t>太平圣惠方 胻骨外，大筋内，筋骨之间</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>횡향 3계통 표, Δ ≤ 15mm 분기 불요</t>
+          <t>약 0~0.5cm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>通考 L3190~3248</t>
+          <t>膝下 3寸</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>한대 근거 없음·通考 过于偏内侧 → 별도 Target 미설정, 기록만</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8절 ①</t>
+          <t>점수</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>papers.id 5·12·19·27·38·46·54·59(PMID 공란)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ST36 연구 15편, PMID/DOI 기재</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>pack_ST36.md, 마스터DB.json</t>
+          <t>Target 1≡3 77.5 ± 0 (B, 이중 채점 승계) / Target 2 56.25 ± 1.25 (C·H, 이중 채점 2026-10-25)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ΔARI 20.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>확정: Target 1≡3 단독 우위(ΔARI-Core 21.25, ± 비중첩). Target 2–3 Δ는 추정 의존(일부 문헌 '胻骨之外约一寸')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8절 ②</t>
+          <t>구판 대응</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>②=2(B3-01 Head zone 근거)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>②=1(L4~S1 vs T6~T9 분절 불일치, 상척수 경로)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>final bcheck n=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>8절 ②</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>③=1, ④=1(B3-11), ⑤=2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>③=2, ④=2(B3-12·15·16·17), ⑤=1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>final bcheck n=3~5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>8절 ②</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>"부합 판정: 확정"</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>"부합", 동물 한정 표지</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>프레임워크 5절 8번</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>8절 ③</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>외부 검색 로그 표</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pack sync_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>9절</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>정의문만</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>$P_{single}$/$P_{comb}$ 실제 분리</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>通考 L3310~3460; 证治通鉴 L1242, L2166</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10절</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>단일 채점 S_orig 85, ARI-Core 79.0, 민감도 78.3, "엄격하게 검증됨"</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>이중 채점 S_orig 81.25, ARI-Core 77.5 ± 0, 민감도 77.1, 범위 제한 결론</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>final_ST36.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>《甲乙经》 심도: DB 10푼 vs 通鉴 인용 "一寸五分"(15푼). 원 《甲乙经》 미대조로 DB값 유지, 이문 병기</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>자침깊이 xlsx 행 121; 通鉴 L3676</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>papers.id 1841 DOI가 저널과 불일치 의심. DB 수정은 하지 않음</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>마스터DB.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>인용 제외</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>pack 랜드마크 papers.id 1700</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>서지 검증 불가(superseded)로 미인용, 체성-자율 반사 틀은 B3-04·B3-05로 인용</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>조정자 통지 2026-10-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>구판 점수</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>구판 v2.6 점수 79.0(비교 불가)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>`_구판_v2.6/` 보고서</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. ARI-Core 77.5 ± 0 (B)·SI 75 불변</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>fma_query.py profile ST36; 보고서 4·6·8절·부록 A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>초음파_참고 시트·그림 4-2 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>앞정강근 공개 초음파 통계, 1896 TI, Rank 6 재실행 로그. 점수 불변</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Marzola 2021; PMID 42500462</t>
+          <t>구 단일 Target(T1) → Target 1≡3; 구 횡향 계통 ①(王冰) → Target 2(신규)</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1353,548 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>머리말</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>프레임워크 문구, "실측 논문 148편 전수 역색인"</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>v2.7 인용 블록, ARI 표기 / 근거 묶음 수치(38·109·39)로 교체</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>final_ST36.json notation, pack_ST36.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>通鉴 목차 조각, 证治通鉴 冲脉 고증 문단, 通考 목차 조각</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>《灵枢·本输》·《素问·针解》·《明堂》 원문과 출처 행</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>通考 `(上)_321-400.md` L3096~3248; 通鉴 `(上卷)_801-880.md` L3410~3692; 证治通鉴 `_1-80.md` L1242, L2162</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2절</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제목뿐인 템플릿</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>시대별 원천/재인용 표</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>같은 원전</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3절</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>"검증된 고전 이명: -"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>三里·下陵·鬼邪·下三里 표</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KJH xlsx 행 122; 通考 L3096~3146; 通鉴 L3412~3428</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4절</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>범용 Layer 경계 2.5/6.5/16.5/22mm, 'Layer 5 관절낭'</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST36 구조 순서(앞정강근→깊은종아리신경·앞정강동정맥→뼈사이막), X·Y 기술, mm 경계는 실측 없음으로 미기재</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>교재 데이터셋; 通考 L3114~3116</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5절</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>공식 설명만</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>문헌별 푼수→mm 계산표</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 행 121; 通鉴 L3676~3692</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6절</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>"2대 교재 일치" 일반문</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>실제 구조명, 피부신경 차이 명시</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>공통교재 refine.xlsx 상세 행 650~655; 김재효 xlsx 상세 행 954~959</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7절</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>규칙 설명만</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>횡향 3계통 표, Δ ≤ 15mm 분기 불요</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>通考 L3190~3248</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8절 ①</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>papers.id 5·12·19·27·38·46·54·59(PMID 공란)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST36 연구 15편, PMID/DOI 기재</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pack_ST36.md, 마스터DB.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>②=2(B3-01 Head zone 근거)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>②=1(L4~S1 vs T6~T9 분절 불일치, 상척수 경로)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>final bcheck n=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>③=1, ④=1(B3-11), ⑤=2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>③=2, ④=2(B3-12·15·16·17), ⑤=1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>final bcheck n=3~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>"부합 판정: 확정"</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>"부합", 동물 한정 표지</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>프레임워크 5절 8번</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8절 ③</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>외부 검색 로그 표</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pack sync_log</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9절</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>정의문만</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>$P_{single}$/$P_{comb}$ 실제 분리</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>通考 L3310~3460; 证治通鉴 L1242, L2166</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10절</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>단일 채점 S_orig 85, ARI-Core 79.0, 민감도 78.3, "엄격하게 검증됨"</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>이중 채점 S_orig 81.25, ARI-Core 77.5 ± 0, 민감도 77.1, 범위 제한 결론</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>final_ST36.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>《甲乙经》 심도: DB 10푼 vs 通鉴 인용 "一寸五分"(15푼). 원 《甲乙经》 미대조로 DB값 유지, 이문 병기</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 행 121; 通鉴 L3676</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>papers.id 1841 DOI가 저널과 불일치 의심. DB 수정은 하지 않음</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>마스터DB.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>인용 제외</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pack 랜드마크 papers.id 1700</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>서지 검증 불가(superseded)로 미인용, 체성-자율 반사 틀은 B3-04·B3-05로 인용</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>조정자 통지 2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>구판 점수</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>구판 v2.6 점수 79.0(비교 불가)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`_구판_v2.6/` 보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. ARI-Core 77.5 ± 0 (B)·SI 75 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile ST36; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>초음파_참고 시트·그림 4-2 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>앞정강근 공개 초음파 통계, 1896 TI, Rank 6 재실행 로그. 점수 불변</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Marzola 2021; PMID 42500462</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7 (문헌스크리닝·ARI_v3.0·분기추론 시트)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3대 원전, 단일 Target(T1), Δ ≤ 15mm 분기 불요</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4대 원전 대조 10행(经络通鉴·证治通鉴 한글번역·通考 현행 편, 파일·행 포인터) 추가; T1→Target 1≡3(점수 불변, ④ 재점검 100 유지); Target 2(王冰 两筋间 근간 중격) 신규 — 10mm 기준으로 T2–T3 분기, 단일 채점(예비) 57.5 (C·H); Tri-Target 좌표·Δ 시트 신설</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARI_v3.0·B-Check·분기추론 (2026-10-25 Target 2 이중 채점)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Target 2 단일 채점(예비) 57.5 (C·H), B-Check 3/12, 분기 판정 예비</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>채점자 B 독립 채점 추가 → Target 2 56.25 ± 1.25 (C·H), 민감도 53.1 (D, 가중치 민감), B-Check 최종 7/12; Target 1≡3 단독 우위 확정</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>정본 Rank 7; 채점자 B(점수 가린 사본 사용)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1566,7 +2353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1618,7 +2405,6 @@
       <c r="B3" t="n">
         <v>3092</v>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1629,7 +2415,6 @@
       <c r="B4" t="n">
         <v>1021</v>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1670,7 +2455,6 @@
       <c r="B7" t="n">
         <v>0.913</v>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1683,7 +2467,6 @@
           <t>anon_1669_3.png</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2477,7 +3260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2520,7 +3303,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2549,7 +3332,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2570,7 +3353,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2591,7 +3374,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2612,12 +3395,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S_orig ④ 通考 교감</t>
+          <t>S_orig ④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2629,11 +3412,16 @@
       <c r="F6" t="n">
         <v>100</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.7.7 재점검: 经络通鉴 下陵→解溪 개찬 교정(13편 L186)·王冰 귀속 교감(20편 L2452) → 100 유지(점수 불변)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2657,7 +3445,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2681,7 +3469,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2712,7 +3500,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>게이트</t>
+          <t>Target 1≡3 게이트</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2724,7 +3512,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARI-Core</t>
+          <t>Target 1≡3 ARI-Core</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2736,7 +3524,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>Target 1≡3 등급</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2748,7 +3536,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>표지</t>
+          <t>Target 1≡3 표지</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2760,7 +3548,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>Target 1≡3 SI</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2770,7 +3558,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>등가중치 민감도</t>
+          <t>Target 1≡3 등가중치 민감도</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2782,7 +3570,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>표기</t>
+          <t>Target 1≡3 표기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2794,12 +3582,341 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>조정</t>
+          <t>Target 1≡3 조정</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>15점 이상 불일치 없음. conflicts 기록(혈위 특이성 반증 B4-04·B4-05, 자극 강도 의존성 B3-16, 위운동 이중 효과 papers.id 34)은 직접 상충이 아니라 적용 범위 제한이므로 B-Check 판정은 '부합'으로 두고 결론에 범위 제한을 병기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S_orig</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>56.25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>59.375</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>하위 ①~④ A 50/50/75/75 · B 50/50/75/50; 차이 6.25 &lt; 15 → 조정 불요, 59.4 ± 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S_orig ① 최초 기술</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>素问·针解 举膝分易见(암시) → 王冰 两筋肉分间(당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S_orig ② 후대 일치율</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B 집계: 穴位通鉴 36조 중 14+부분 3 = 39~47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S_orig ③ 이명 해소</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>75</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>혈 단위 판정과 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S_orig ④ 通考·经络通鉴 교감</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>75</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A 표현 이문(75) / B Target 2 특유 문헌 문제 5건 미해소(50): 甲乙 주 혼입 L2150, 铜人 卷上·卷下 모순 L2166·L2168, 穴位通鉴 L2614 귀속, 聚英·大成 병합 L2188, 经络通鉴 01편 L383</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S_clarity</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>75</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경계 구조 2대 교재 같은 단면 일치 + B1 근간 중격</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S_reflex</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>위치 특이 Layer A 0편 → 게이트 2(H); B-Check A 3 · B 7 → 최종 7/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SI (S_safety)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>별도</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>중격 직자 시 Layer 4(깊은종아리신경·앞정강동맥) 직접 접촉</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Target 2 ARI-Core</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>56.25 ± 1.25 (C·H)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A 0.40×62.5+0.35×75+0.25×25 = 57.5 / B 0.40×56.25+0.35×75+0.25×25 = 55.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Target 2 민감도</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>53.1 (D, 가중치 민감)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A 54.2 / B 52.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Target 2 표기</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ARI v3.0 | ARI-Core 56.25 ± 1.25 (C·H) | SI 50 | 잠정 가중치 0.40/0.35/0.25 | 민감도(등가중치): 53.1 (D, 가중치 민감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>분기 판정(확정)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Target 1≡3 77.5 ± 0 [77.5] vs Target 2 56.25 ± 1.25 [55.0, 57.5] → ΔARI-Core 21.25 ≥ 10, ± 비중첩 → Target 1≡3 단독 우위 확정(2026-10-25 이중 채점)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tri-Target 판정 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>후속 과제</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>papers.id 1341(WHO 위치 초음파: 앞정강동맥 24mm, 목표 22mm) → Target 1≡3 S_clarity·SI 재검토; papers.id 1203(허임 「訛穴」 兩筋間陷中) 1절 보강; 楼新法 2006 《中国针灸》 26(7):483–486 Layer A 확보; 刺法论은 송대 遗篇</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3082,6 +4199,140 @@
         <is>
           <t>판정: 부합 (③~⑤ 동물 한정)</t>
         </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Target 2 B-Check (2026-10-25 이중 채점)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>최종(7/12 미부합)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>① 말초 실체</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>② 분절 정합</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>③ 구심 섬유·수용체</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>④ 중추 중계</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>⑤ 원심 효과</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>⑥ 인체 전환</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/ST_족양명위경/ST36_족삼리/ST36_족삼리_해부생리_분석데이터.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초음파_참고" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고전정위_가로3계통" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초음파_참고" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1140,7 +1144,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>经络通鉴 19편 L253·L449; 通考 L307</t>
+          <t>经络通鉴 19편 L253·L449; 通考 L307; 《铜人》 卷上 胻骨外大筋内(通考 L243·L307 셋째 계통)</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1156,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>王冰 胻外两筋肉分间 / 铜人卷下·圣济 胻外廉两筋间 = 앞정강근(FMA:22532)–긴발가락폄근(FMA:22534) 근간 중격</t>
+          <t>王冰 胻外两筋肉分间 / 铜人卷下·圣济 胻外廉两筋间 = 앞정강근(FMA:22532)–긴발가락폄근(FMA:22534) 근간 중격 / 「訛穴」 銅曰…兩筋間陷中·自骨邊橫量一寸(papers.id 1203)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>通考 L215·L231 (현행 편)</t>
+          <t>通考 L215·L231 (현행 편); papers.id 1203 p.38</t>
         </is>
       </c>
     </row>
@@ -1358,534 +1362,459 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>계통</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>원래 내용</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>바꾼 내용</t>
+          <t>문헌(시대)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>원문</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>해부 위치(추정)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>근거 포인터(내부)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>판정·비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>머리말</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>프레임워크 문구, "실측 논문 148편 전수 역색인"</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>v2.7 인용 블록, ARI 표기 / 근거 묶음 수치(38·109·39)로 교체</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>final_ST36.json notation, pack_ST36.md</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ⓞ 고전 원문</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>《灵枢·本输》·《黄帝明堂经》(한)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>下陵膝下三寸，胻骨外三里也 / 在膝下三寸，胻外廉</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>정강뼈 바깥 가장자리 쪽(횡향 미특정)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>通考 08편 L183·L191; 经络通鉴 19편 L253·L449</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>원천</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1절</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>通鉴 목차 조각, 证治通鉴 冲脉 고증 문단, 通考 목차 조각</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>《灵枢·本输》·《素问·针解》·《明堂》 원문과 출처 행</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>通考 `(上)_321-400.md` L3096~3248; 通鉴 `(上卷)_801-880.md` L3410~3692; 证治通鉴 `_1-80.md` L1242, L2162</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>③ 대근내(大筋内)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>《铜人腧穴针灸图经》 卷上(송)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸，胻骨外大筋内宛宛中(2:23)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>앞정강근 근복(《通考》 셋째 계통 = 현대 정위)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>穴位通鉴 19편 L2166; 通考 08편 L243·L307</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>《铜人》 한 책 안의 첫째 정위</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2절</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>제목뿐인 템플릿</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>시대별 원천/재인용 표</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>같은 원전</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>③ 대근내(大筋内)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>《神应经》(명)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>在膝盖下三寸，胻骨间大筋内，坐而取之</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>앞정강근 근복</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>穴位通鉴 19편 L2180; 通考 08편 L255</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>'膝盖下' — 王執中 '너무 높음' 경고 대상</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3절</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>"검증된 고전 이명: -"</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>三里·下陵·鬼邪·下三里 표</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>KJH xlsx 행 122; 通考 L3096~3146; 通鉴 L3412~3428</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>③ 대근내(大筋内)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>《東醫寶鑑》 鍼灸篇(조선, 1613)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸䯒骨外大筋內宛宛中(銅人)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>앞정강근 근복</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>G:/내 드라이브/도서 번역/01_도서_번역_및_원전/동의보감/동의보감_111_鍼灸篇_鍼灸.md L395</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>卷上을 인용</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4절</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>범용 Layer 경계 2.5/6.5/16.5/22mm, 'Layer 5 관절낭'</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ST36 구조 순서(앞정강근→깊은종아리신경·앞정강동정맥→뼈사이막), X·Y 기술, mm 경계는 실측 없음으로 미기재</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>교재 데이터셋; 通考 L3114~3116</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>① 양근간(兩筋間)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>王冰 《素问》 주(당)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸，胻外两筋肉分间。极重按之，则足跗上动脉止矣</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>TA–EDL 근간 중격</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>穴位通鉴 19편 L2158; 通考 08편 L215; 经络通鉴 1편 L2015~2017</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>촉진 표현의 원천. 동맥 압박 소견</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5절</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>공식 설명만</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>문헌별 푼수→mm 계산표</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>자침깊이 xlsx 행 121; 通鉴 L3676~3692</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>① 양근간(兩筋間)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>《铜人腧穴针灸图经》 卷下(송)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸，胻外廉两筋间，当举足取之 / 可灸三壮，针入五分(5:72)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>TA–EDL 근간 중격</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>穴位通鉴 19편 L2168; 通考 08편 L231·L773</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>《铜人》 한 책 안의 둘째 정위. 5푼=11.5mm(Target 2 심도 상한)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6절</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>"2대 교재 일치" 일반문</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>실제 구조명, 피부신경 차이 명시</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>공통교재 refine.xlsx 상세 행 650~655; 김재효 xlsx 상세 행 954~959</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>① 양근간(兩筋間)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>《圣济总录》·《针灸资生经》(송)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸胻外廉两筋间，当举足取之 / 犊鼻之下三寸方是三里</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>TA–EDL 근간 중격</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>穴位通鉴 19편 L2106·L2170</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>卷下 계통 재인용; 종향 교감</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7절</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>규칙 설명만</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>횡향 3계통 표, Δ ≤ 15mm 분기 불요</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>通考 L3190~3248</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>① 양근간(兩筋間)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>《東醫寶鑑》 鍼灸篇(조선, 1613)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸陷中䯒骨外廉兩筋肉分間(內經) … 深則足趺陽脉不見 按之大衝脉不動是正穴</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>TA–EDL 근간 중격</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>동의보감_111_鍼灸篇_鍼灸.md L395</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>출처 표지 오류: 王冰 주를 (內經)으로 표지</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>8절 ①</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>papers.id 5·12·19·27·38·46·54·59(PMID 공란)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ST36 연구 15편, PMID/DOI 기재</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>pack_ST36.md, 마스터DB.json</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>① 양근간(兩筋間)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>허임 《鍼灸經驗方》 「訛穴」(조선, 1644)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>銅曰在膝蓋下三寸䯒骨外廉兩筋間陷中 … 自骨邊橫量一寸 該的兩筋間陷中 以手按兩筋間 則足跗上太衝脈不動 … 而俗徒取䯒外廉陷中</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>TA–EDL 근간 중격(뼈 가장자리에서 약 1촌, 촉진으로 확정)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>papers.id 1203 (이연희 2008, 경락경혈학회지 25(4):31–47) p.38·p.44·p.46; G:/내 드라이브/학습자료/실험 및 연구 논문/2008_경락경혈학회지_이연희_…pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>사용자 제시 문구의 원출처. 《铜人》 원문 아님(卷下 개변 인용). 속간 '䯒外廉陷中'을 오류로 지적; 이연희 2008은 WHO 'on TA'를 같은 오류로 봄</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>8절 ②</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>②=2(B3-01 Head zone 근거)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>②=1(L4~S1 vs T6~T9 분절 불일치, 상척수 경로)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>final bcheck n=2</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>② 내측 편위</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>기록만(Target 제외)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>《太平圣惠方》(송)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>在膝下三寸，胻骨外大筋内筋骨之间陷者宛宛中</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>정강뼈 가쪽면–앞정강근 사이</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>通考 08편 L199; 穴位通鉴 19편 L2164</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>《通考》 过于偏内侧</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>8절 ②</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>③=1, ④=1(B3-11), ⑤=2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>③=2, ④=2(B3-12·15·16·17), ⑤=1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>final bcheck n=3~5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>8절 ②</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>"부합 판정: 확정"</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>"부합", 동물 한정 표지</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>프레임워크 5절 8번</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>8절 ③</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>외부 검색 로그 표</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pack sync_log</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>9절</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>정의문만</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>$P_{single}$/$P_{comb}$ 실제 분리</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>通考 L3310~3460; 证治通鉴 L1242, L2166</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10절</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>단일 채점 S_orig 85, ARI-Core 79.0, 민감도 78.3, "엄격하게 검증됨"</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>이중 채점 S_orig 81.25, ARI-Core 77.5 ± 0, 민감도 77.1, 범위 제한 결론</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>final_ST36.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>《甲乙经》 심도: DB 10푼 vs 通鉴 인용 "一寸五分"(15푼). 원 《甲乙经》 미대조로 DB값 유지, 이문 병기</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>자침깊이 xlsx 행 121; 通鉴 L3676</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>papers.id 1841 DOI가 저널과 불일치 의심. DB 수정은 하지 않음</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>마스터DB.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>인용 제외</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>pack 랜드마크 papers.id 1700</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>서지 검증 불가(superseded)로 미인용, 체성-자율 반사 틀은 B3-04·B3-05로 인용</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>조정자 통지 2026-10-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>구판 점수</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>구판 v2.6 점수 79.0(비교 불가)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>`_구판_v2.6/` 보고서</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. ARI-Core 77.5 ± 0 (B)·SI 75 불변</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>fma_query.py profile ST36; 보고서 4·6·8절·부록 A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>초음파_참고 시트·그림 4-2 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>앞정강근 공개 초음파 통계, 1896 TI, Rank 6 재실행 로그. 점수 불변</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Marzola 2021; PMID 42500462</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-25 Framework 2.7.7 (문헌스크리닝·ARI_v3.0·분기추론 시트)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3대 원전, 단일 Target(T1), Δ ≤ 15mm 분기 불요</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4대 원전 대조 10행(经络通鉴·证治通鉴 한글번역·通考 현행 편, 파일·행 포인터) 추가; T1→Target 1≡3(점수 불변, ④ 재점검 100 유지); Target 2(王冰 两筋间 근간 중격) 신규 — 10mm 기준으로 T2–T3 분기, 단일 채점(예비) 57.5 (C·H); Tri-Target 좌표·Δ 시트 신설</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Framework 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ARI_v3.0·B-Check·분기추론 (2026-10-25 Target 2 이중 채점)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Target 2 단일 채점(예비) 57.5 (C·H), B-Check 3/12, 분기 판정 예비</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>채점자 B 독립 채점 추가 → Target 2 56.25 ± 1.25 (C·H), 민감도 53.1 (D, 가중치 민감), B-Check 최종 7/12; Target 1≡3 단독 우위 확정</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>정본 Rank 7; 채점자 B(점수 가린 사본 사용)</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>현대</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>교재·WHO</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>犊鼻下3寸，胫骨前嵴外一横指，胫骨前肌中</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>앞정강근 근복</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>通考 08편 L295~303·L307</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>이연희 2008 반론 병기</t>
         </is>
       </c>
     </row>
@@ -1895,6 +1824,570 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>머리말</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>프레임워크 문구, "실측 논문 148편 전수 역색인"</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>v2.7 인용 블록, ARI 표기 / 근거 묶음 수치(38·109·39)로 교체</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>final_ST36.json notation, pack_ST36.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>通鉴 목차 조각, 证治通鉴 冲脉 고증 문단, 通考 목차 조각</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>《灵枢·本输》·《素问·针解》·《明堂》 원문과 출처 행</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>通考 `(上)_321-400.md` L3096~3248; 通鉴 `(上卷)_801-880.md` L3410~3692; 证治通鉴 `_1-80.md` L1242, L2162</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2절</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>제목뿐인 템플릿</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>시대별 원천/재인용 표</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>같은 원전</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3절</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>"검증된 고전 이명: -"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>三里·下陵·鬼邪·下三里 표</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KJH xlsx 행 122; 通考 L3096~3146; 通鉴 L3412~3428</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4절</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>범용 Layer 경계 2.5/6.5/16.5/22mm, 'Layer 5 관절낭'</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST36 구조 순서(앞정강근→깊은종아리신경·앞정강동정맥→뼈사이막), X·Y 기술, mm 경계는 실측 없음으로 미기재</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>교재 데이터셋; 通考 L3114~3116</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5절</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>공식 설명만</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>문헌별 푼수→mm 계산표</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 행 121; 通鉴 L3676~3692</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6절</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>"2대 교재 일치" 일반문</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>실제 구조명, 피부신경 차이 명시</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>공통교재 refine.xlsx 상세 행 650~655; 김재효 xlsx 상세 행 954~959</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7절</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>규칙 설명만</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>횡향 3계통 표, Δ ≤ 15mm 분기 불요</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>通考 L3190~3248</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8절 ①</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>papers.id 5·12·19·27·38·46·54·59(PMID 공란)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST36 연구 15편, PMID/DOI 기재</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pack_ST36.md, 마스터DB.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>②=2(B3-01 Head zone 근거)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>②=1(L4~S1 vs T6~T9 분절 불일치, 상척수 경로)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>final bcheck n=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>③=1, ④=1(B3-11), ⑤=2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>③=2, ④=2(B3-12·15·16·17), ⑤=1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>final bcheck n=3~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8절 ②</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>"부합 판정: 확정"</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>"부합", 동물 한정 표지</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>프레임워크 5절 8번</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8절 ③</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>외부 검색 로그 표</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pack sync_log</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9절</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>정의문만</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>$P_{single}$/$P_{comb}$ 실제 분리</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>通考 L3310~3460; 证治通鉴 L1242, L2166</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10절</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>단일 채점 S_orig 85, ARI-Core 79.0, 민감도 78.3, "엄격하게 검증됨"</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>이중 채점 S_orig 81.25, ARI-Core 77.5 ± 0, 민감도 77.1, 범위 제한 결론</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>final_ST36.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>《甲乙经》 심도: DB 10푼 vs 通鉴 인용 "一寸五分"(15푼). 원 《甲乙经》 미대조로 DB값 유지, 이문 병기</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 행 121; 通鉴 L3676</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>papers.id 1841 DOI가 저널과 불일치 의심. DB 수정은 하지 않음</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>마스터DB.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>인용 제외</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pack 랜드마크 papers.id 1700</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>서지 검증 불가(superseded)로 미인용, 체성-자율 반사 틀은 B3-04·B3-05로 인용</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>조정자 통지 2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>구판 점수</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>구판 v2.6 점수 79.0(비교 불가)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`_구판_v2.6/` 보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. ARI-Core 77.5 ± 0 (B)·SI 75 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile ST36; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>초음파_참고 시트·그림 4-2 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>앞정강근 공개 초음파 통계, 1896 TI, Rank 6 재실행 로그. 점수 불변</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Marzola 2021; PMID 42500462</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7 (문헌스크리닝·ARI_v3.0·분기추론 시트)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3대 원전, 단일 Target(T1), Δ ≤ 15mm 분기 불요</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4대 원전 대조 10행(经络通鉴·证治通鉴 한글번역·通考 현행 편, 파일·행 포인터) 추가; T1→Target 1≡3(점수 불변, ④ 재점검 100 유지); Target 2(王冰 两筋间 근간 중격) 신규 — 10mm 기준으로 T2–T3 분기, 단일 채점(예비) 57.5 (C·H); Tri-Target 좌표·Δ 시트 신설</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARI_v3.0·B-Check·분기추론 (2026-10-25 Target 2 이중 채점)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Target 2 단일 채점(예비) 57.5 (C·H), B-Check 3/12, 분기 판정 예비</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>채점자 B 독립 채점 추가 → Target 2 56.25 ± 1.25 (C·H), 민감도 53.1 (D, 가중치 민감), B-Check 최종 7/12; Target 1≡3 단독 우위 확정</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>정본 Rank 7; 채점자 B(점수 가린 사본 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26 고전 정위 정밀화 (고전정위_가로3계통 시트 신설·분기추론 보강)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>《铜人》 卷上·卷下 미분리, "銅曰…兩筋間陷中" 출처 미확인, 그림 4-1 단일 경로</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>'銅曰…' = 허임 《鍼灸經驗方》 「訛穴」의 《铜人》 卷下 개변 인용으로 판별; 《铜人》 卷上(Target 1≡3)·卷下(Target 2) 분리; 《東醫寶鑑》 (內經) 표지 오류 기록; 그림 4-1 가로 3계통 개정. ARI 점수 불변</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>papers.id 1203 p.38·44·46; 穴位通鉴 19편 L2166~2180; 通考 08편 L231~255·L307·L773; 经络通鉴 1편 L2015~2017; 동의보감 鍼灸篇</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2353,7 +2846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
